--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alanv\Proyecto-SP\Reuniones\Asistencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75F7E38-3259-4F03-8168-79BDC1ED297C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A10024-2873-4FD4-89DE-C7C9719DFC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{7ACB4728-31AA-401E-9FB6-82724269CEE0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="26">
   <si>
     <t>Fecha Asistencia</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>Asignación de tareas, push de la nave amiga y puesta para revisión.</t>
+  </si>
+  <si>
+    <t>Ha hecho la revisión de todas las clases terminadas</t>
+  </si>
+  <si>
+    <t>Asignación de nuevas tareas</t>
   </si>
 </sst>
 </file>
@@ -488,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8916078C-F631-4E21-92AE-D86B11F135E7}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
@@ -659,49 +665,89 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>46073</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46074</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>46076</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46075</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>46077</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46076</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>46078</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -709,9 +755,9 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -720,9 +766,7 @@
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>46079</v>
-      </c>
+      <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -730,9 +774,7 @@
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>46080</v>
-      </c>
+      <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -740,9 +782,7 @@
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>46081</v>
-      </c>
+      <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -766,28 +806,28 @@
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
@@ -805,30 +845,6 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alanv\Proyecto-SP\Reuniones\Asistencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A10024-2873-4FD4-89DE-C7C9719DFC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B363AA-400E-4450-BBC2-2A1F204D896C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{7ACB4728-31AA-401E-9FB6-82724269CEE0}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15885" xr2:uid="{7ACB4728-31AA-401E-9FB6-82724269CEE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Primer_Sprint" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
   <si>
     <t>Fecha Asistencia</t>
   </si>
@@ -114,6 +114,15 @@
   </si>
   <si>
     <t>Asignación de nuevas tareas</t>
+  </si>
+  <si>
+    <t>Ha hecho la clase de Batallón con sus atributos y métodos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merges de las ramas nuevas con la rama develop junto a creación de la clase Escuadrón con sus métodos y atributos  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin presentar, ha hecho  el método pintar y comprobar colisiones en el contralador </t>
   </si>
 </sst>
 </file>
@@ -749,11 +758,21 @@
       <c r="A13" s="3">
         <v>46079</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">

--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alanv\Proyecto-SP\Reuniones\Asistencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B363AA-400E-4450-BBC2-2A1F204D896C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9D3A99-C811-4920-B86A-3248658DAE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15885" xr2:uid="{7ACB4728-31AA-401E-9FB6-82724269CEE0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="32">
   <si>
     <t>Fecha Asistencia</t>
   </si>
@@ -123,6 +123,15 @@
   </si>
   <si>
     <t xml:space="preserve">Sin presentar, ha hecho  el método pintar y comprobar colisiones en el contralador </t>
+  </si>
+  <si>
+    <t>Ha hecho la clase de Batallón con sus atributos y métodos(Corregidos)</t>
+  </si>
+  <si>
+    <t>Clase Escuadron con sus atributos y métodos(Corregidos)</t>
+  </si>
+  <si>
+    <t>Ha hecho todo el controlador y el test primarios.</t>
   </si>
 </sst>
 </file>
@@ -778,14 +787,26 @@
       <c r="A14" s="3">
         <v>46080</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>46081</v>
+      </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>

--- a/Reuniones/Asistencia/Asistencia_Sprints.xlsx
+++ b/Reuniones/Asistencia/Asistencia_Sprints.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alanv\Proyecto-SP\Reuniones\Asistencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9D3A99-C811-4920-B86A-3248658DAE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E56ECB1-1959-418F-A677-EBB3B17DBE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15885" xr2:uid="{7ACB4728-31AA-401E-9FB6-82724269CEE0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="35">
   <si>
     <t>Fecha Asistencia</t>
   </si>
@@ -132,6 +132,15 @@
   </si>
   <si>
     <t>Ha hecho todo el controlador y el test primarios.</t>
+  </si>
+  <si>
+    <t>Ajustar la invocación del batallón y retirar los métodos de colisión ademas de poner bien el título e icono del juego</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probar los metodos disparar, para centrar los disparos</t>
+  </si>
+  <si>
+    <t>Hacer arreglos en el Main, también para que funcione en android cambiar el gradlle del juego.  Merge Final para terminar el proyecto a la rama develop</t>
   </si>
 </sst>
 </file>
@@ -803,15 +812,25 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>46081</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
